--- a/Results/TestCases/XLSX/dashboard_TestCases.xlsx
+++ b/Results/TestCases/XLSX/dashboard_TestCases.xlsx
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_DASH_02</t>
@@ -246,7 +246,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -265,7 +265,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>

--- a/Results/TestCases/XLSX/dashboard_TestCases.xlsx
+++ b/Results/TestCases/XLSX/dashboard_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="114">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,13 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The header text should equal 'Dashboard'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,18 +79,28 @@
     <t>Verify dashboard widgets are visible</t>
   </si>
   <si>
+    <t xml:space="preserve">- The widget count should be greater than '0'
+- The visible should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_DASH_03</t>
   </si>
   <si>
     <t>Verify Time at Work widget is displayed</t>
   </si>
   <si>
+    <t>- The 'Time at Work' widget should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_04</t>
   </si>
   <si>
     <t>Verify My Actions widget is displayed</t>
   </si>
   <si>
+    <t>- The 'My Actions' widget should be visible</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -102,124 +110,265 @@
     <t>Verify Quick Launch widget is displayed</t>
   </si>
   <si>
+    <t>- The 'Quick Launch' widget should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_06</t>
   </si>
   <si>
     <t>Verify sidebar contains all main navigation items</t>
   </si>
   <si>
+    <t>- The dashboard page.sidebar link(module name) should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_07</t>
   </si>
   <si>
     <t>Verify logged-in user name is displayed in header</t>
   </si>
   <si>
+    <t>- The length should be greater than '0'</t>
+  </si>
+  <si>
     <t>TC_DASH_08</t>
   </si>
   <si>
     <t>Verify user dropdown shows About, Support, Change Password, Logout</t>
   </si>
   <si>
+    <t>1. Open the user profile dropdown menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The About link should be visible
+- The Support link should be visible
+- The Change Password link should be visible
+- The Logout link should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_09</t>
   </si>
   <si>
     <t>Verify sidebar collapse and expand functionality</t>
   </si>
   <si>
+    <t>1. Click the sidebar collapse toggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The sidebar navigation panel should be visible
+- The sidebar navigation panel should have a CSS class matching a value matching /toggled/
+- The sidebar navigation panel should not have a CSS class matching a value matching /toggled/</t>
+  </si>
+  <si>
     <t>TC_DASH_10</t>
   </si>
   <si>
     <t>Verify Employees on Leave Today widget is displayed</t>
   </si>
   <si>
+    <t>- The 'Employees on Leave Today' widget should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_11</t>
   </si>
   <si>
     <t>Verify sidebar search filters navigation items</t>
   </si>
   <si>
+    <t>1. Type into the sidebar module search box</t>
+  </si>
+  <si>
+    <t>- The dashboard page.sidebar link('admin') should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_12</t>
   </si>
   <si>
     <t>Verify dashboard URL contains correct path</t>
   </si>
   <si>
+    <t>- The dashboard page.page.url() should contain '/dashboard/index'</t>
+  </si>
+  <si>
     <t>TC_DASH_13</t>
   </si>
   <si>
     <t>Verify user profile dropdown image has valid attributes</t>
   </si>
   <si>
+    <t xml:space="preserve">- The img should be visible
+- The src should not be null
+- The length should be greater than '0'
+- The width should be greater than '0'
+- The height should be greater than '0'</t>
+  </si>
+  <si>
     <t>TC_DASH_14</t>
   </si>
   <si>
     <t>Verify corporate branding logo is visible in sidebar header</t>
   </si>
   <si>
+    <t>- The brand should be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_15</t>
   </si>
   <si>
     <t>Verify sidebar search input is functional</t>
   </si>
   <si>
+    <t xml:space="preserve">- The sidebar search field should be visible
+- The placeholder should equal 'Search'</t>
+  </si>
+  <si>
     <t>TC_DASH_16</t>
   </si>
   <si>
     <t>Verify dashboard widgets have correct card container CSS classes</t>
   </si>
   <si>
+    <t>- The first widget should have a CSS class matching a value matching /orangehrm-dashboard-widget/</t>
+  </si>
+  <si>
     <t>TC_DASH_17</t>
   </si>
   <si>
     <t>Verify Assign Leave link in Quick Launch redirects properly</t>
   </si>
   <si>
+    <t>1. Click the 'Assign Leave' element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/leave/assignLeave'</t>
+  </si>
+  <si>
     <t>TC_DASH_18</t>
   </si>
   <si>
     <t>Verify Leave List link in Quick Launch redirects properly</t>
   </si>
   <si>
+    <t>1. Click the 'Leave List' element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/leave/viewLeaveList'</t>
+  </si>
+  <si>
     <t>TC_DASH_19</t>
   </si>
   <si>
     <t>Verify Timesheets link in Quick Launch redirects properly</t>
   </si>
   <si>
+    <t>1. Click the 'Timesheets' element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/time/viewEmployeeTimesheet'</t>
+  </si>
+  <si>
     <t>TC_DASH_20</t>
   </si>
   <si>
     <t>Verify Apply Leave link in Quick Launch redirects properly</t>
   </si>
   <si>
+    <t>1. Click the 'Apply Leave' element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/leave/applyLeave'</t>
+  </si>
+  <si>
     <t>TC_DASH_21</t>
   </si>
   <si>
     <t>Verify My Leave link in Quick Launch redirects properly</t>
   </si>
   <si>
+    <t>1. Click the 'My Leave' element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/leave/viewMyLeaveList'</t>
+  </si>
+  <si>
     <t>TC_DASH_22</t>
   </si>
   <si>
     <t>Verify My Timesheet link in Quick Launch redirects properly</t>
   </si>
   <si>
+    <t>1. Click the 'My Timesheet' element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/time/viewMyTimesheet'</t>
+  </si>
+  <si>
     <t>TC_DASH_23</t>
   </si>
   <si>
     <t>Verify Support option opens support page</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Open the user profile dropdown menu
+2. Click the Support link</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/help/support'</t>
+  </si>
+  <si>
     <t>TC_DASH_24</t>
   </si>
   <si>
     <t>Verify About link displays modal pop-up</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Open the user profile dropdown menu
+2. Click the About link
+3. Click the oxd dialog close button element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The modal should be visible
+- The modal should not be visible</t>
+  </si>
+  <si>
     <t>TC_DASH_25</t>
   </si>
   <si>
     <t>Verify dashboard topbar has header with correct tags</t>
+  </si>
+  <si>
+    <t>- The title should be visible</t>
+  </si>
+  <si>
+    <t>TC_DASH_26</t>
+  </si>
+  <si>
+    <t>Verify Buzz Latest Posts widget is displayed on dashboard</t>
+  </si>
+  <si>
+    <t>- The 'Buzz Latest Posts' widget should be visible</t>
+  </si>
+  <si>
+    <t>TC_DASH_27</t>
+  </si>
+  <si>
+    <t>Verify sidebar search with a non-existent module name shows no matching navigation link</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>- The oxd main menu item element should equal '0'</t>
+  </si>
+  <si>
+    <t>TC_DASH_28</t>
+  </si>
+  <si>
+    <t>Verify user dropdown menu closes after selecting Escape or clicking elsewhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The Logout link should be visible
+- The Logout link should not be visible</t>
   </si>
 </sst>
 </file>
@@ -657,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -766,7 +915,7 @@
         <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -777,7 +926,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -786,13 +935,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -801,7 +950,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -812,7 +961,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -821,13 +970,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -836,10 +985,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -847,7 +996,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -856,13 +1005,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -871,10 +1020,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -882,7 +1031,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -891,13 +1040,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -906,10 +1055,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -917,7 +1066,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -926,13 +1075,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -941,10 +1090,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -952,7 +1101,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -961,25 +1110,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -987,7 +1136,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -996,25 +1145,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1022,7 +1171,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1031,13 +1180,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1046,10 +1195,10 @@
         <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1057,7 +1206,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1066,25 +1215,25 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1092,7 +1241,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1101,13 +1250,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1116,10 +1265,10 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1127,7 +1276,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1136,13 +1285,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1151,10 +1300,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1162,7 +1311,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1171,13 +1320,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1186,10 +1335,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1197,7 +1346,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1206,13 +1355,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1221,10 +1370,10 @@
         <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1232,7 +1381,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1241,13 +1390,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1256,10 +1405,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1267,7 +1416,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1276,25 +1425,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1302,7 +1451,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1311,25 +1460,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1337,7 +1486,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1346,25 +1495,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1372,7 +1521,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1381,25 +1530,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1407,7 +1556,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1416,25 +1565,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1442,7 +1591,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1451,25 +1600,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1477,7 +1626,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1486,25 +1635,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1512,7 +1661,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1521,25 +1670,25 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1547,7 +1696,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1556,13 +1705,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1571,12 +1720,117 @@
         <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Results/TestCases/XLSX/dashboard_TestCases.xlsx
+++ b/Results/TestCases/XLSX/dashboard_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="115">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -81,6 +81,9 @@
   <si>
     <t xml:space="preserve">- The widget count should be greater than '0'
 - The visible should equal 'true'</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_DASH_03</t>
@@ -375,7 +378,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -399,8 +402,14 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,6 +424,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -465,6 +479,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -920,13 +937,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -935,13 +952,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -950,18 +967,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -970,13 +987,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -985,10 +1002,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -996,7 +1013,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -1005,13 +1022,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -1020,10 +1037,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -1031,7 +1048,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -1040,13 +1057,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -1055,10 +1072,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -1066,7 +1083,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -1075,13 +1092,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -1090,10 +1107,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -1101,7 +1118,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1110,25 +1127,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -1136,7 +1153,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1145,25 +1162,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1171,7 +1188,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1180,13 +1197,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1195,10 +1212,10 @@
         <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1206,7 +1223,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1215,25 +1232,25 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1241,7 +1258,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1250,13 +1267,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1265,10 +1282,10 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1276,7 +1293,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1285,13 +1302,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1300,10 +1317,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1311,7 +1328,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1320,13 +1337,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1335,10 +1352,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1346,7 +1363,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1355,13 +1372,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1370,10 +1387,10 @@
         <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1381,7 +1398,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1390,13 +1407,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1405,10 +1422,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1416,7 +1433,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1425,25 +1442,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1451,7 +1468,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1460,25 +1477,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1486,7 +1503,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1495,25 +1512,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1521,7 +1538,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1530,25 +1547,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1556,7 +1573,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1565,25 +1582,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1591,7 +1608,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1600,25 +1617,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1626,7 +1643,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1635,25 +1652,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1661,7 +1678,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1670,25 +1687,25 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1696,7 +1713,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1705,13 +1722,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1720,10 +1737,10 @@
         <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>19</v>
@@ -1731,7 +1748,7 @@
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1740,13 +1757,13 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -1755,10 +1772,10 @@
         <v>16</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>19</v>
@@ -1766,7 +1783,7 @@
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1775,25 +1792,25 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>19</v>
@@ -1801,7 +1818,7 @@
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
@@ -1810,25 +1827,25 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>19</v>
